--- a/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_FCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_FCP.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Bropleh (14 L)</t>
+          <t>C. Allen Williams (26 L)</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Bropleh (8.0 3PA)</t>
+          <t>T. Bropleh (13.0 3PA)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T. Bropleh (1.714)</t>
+          <t>T. Bropleh (1.583)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Restricted Area (31 L)</t>
+          <t>Above the Break 3 (44 L)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Restricted Area (80.6%)</t>
+          <t>Restricted Area (78.6%)</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -592,7 +592,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -930,227 +930,237 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>321972</t>
+          <t>317922</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
         <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>65.4%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
         <v>6</v>
       </c>
-      <c r="L2" t="n">
+      <c r="AY2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>900.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
         <v>6</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.714285714285714</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>6</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>1</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -1172,126 +1182,136 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>317922</t>
+          <t>321972</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
+        <v>38</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>11</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>6</v>
-      </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>13</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>11</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V3" t="n">
-        <v>5</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="AE3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="Y3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AH3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
@@ -1301,11 +1321,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1314,24 +1334,24 @@
         </is>
       </c>
       <c r="AQ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
         <v>3</v>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AV3" t="n">
@@ -1339,14 +1359,14 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
@@ -1358,27 +1378,27 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>800.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BD3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -1418,152 +1438,172 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="K4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>8</v>
       </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.75</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="V4" t="n">
-        <v>5</v>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="AB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AE4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AH4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AE4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AK4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AN4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AT4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
@@ -1571,18 +1611,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
@@ -1590,31 +1630,959 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
+          <t>1000.0%</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
           <t>600.0%</t>
         </is>
       </c>
-      <c r="BC4" t="n">
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>305553</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>19</v>
+      </c>
+      <c r="H5" t="n">
         <v>9</v>
       </c>
-      <c r="BD4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE4" t="inlineStr">
+      <c r="I5" t="n">
+        <v>23</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.210526315789474</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>600.0%</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FCP_M._QUEIROZ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>154371</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>M. Queiroz</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>17</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="BG4" t="n">
+      <c r="BC6" t="n">
         <v>3</v>
       </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BD6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FCP_G._DELGADO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>223738</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>G. Delgado</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW7" t="inlineStr">
         <is>
           <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>900.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>321973</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>500.0%</t>
         </is>
       </c>
     </row>
@@ -1629,7 +2597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1658,7 +2626,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -1676,7 +2644,7 @@
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -2028,107 +2996,107 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>13</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.714285714285714</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>6</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="AE2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -2153,11 +3121,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -2175,23 +3143,23 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
         <v>2</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -2202,11 +3170,11 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -2221,20 +3189,20 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="BG2" t="n">
         <v>1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -2256,121 +3224,121 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_M._QUEIROZ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>317922</t>
+          <t>154371</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>M. Queiroz</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
+        <v>17</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>11</v>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" t="n">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
         <v>4</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
         <v>6</v>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>5</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>5</v>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -2381,84 +3349,84 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AN3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="AV3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
         <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="BA3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>800.0%</t>
-        </is>
-      </c>
       <c r="BC3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD3" t="n">
         <v>8</v>
       </c>
-      <c r="BD3" t="n">
-        <v>2</v>
-      </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
@@ -2466,7 +3434,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2488,74 +3456,74 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FCP_C._DUNDAO</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>322305</t>
+          <t>305553</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C. Dundao</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>10</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.9090909090909091</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -2563,46 +3531,46 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="AE4" t="n">
         <v>5</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -2613,7 +3581,7 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -2621,48 +3589,48 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
         <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
@@ -2670,7 +3638,7 @@
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -2678,19 +3646,19 @@
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
@@ -2699,6 +3667,974 @@
       <c r="BH4" t="inlineStr">
         <is>
           <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FCP_G._DELGADO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>223738</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>G. Delgado</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>900.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>321973</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>317922</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>17</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>65.4%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>8</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>900.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>322305</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>15</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>12</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AV8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>1000.0%</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BG8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>600.0%</t>
         </is>
       </c>
     </row>
@@ -2713,7 +4649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2742,7 +4678,7 @@
     <col width="19" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -2758,6 +4694,2058 @@
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="23" customWidth="1" min="48" max="48"/>
+    <col width="18" customWidth="1" min="49" max="49"/>
+    <col width="24" customWidth="1" min="50" max="50"/>
+    <col width="22" customWidth="1" min="51" max="51"/>
+    <col width="19" customWidth="1" min="52" max="52"/>
+    <col width="27" customWidth="1" min="53" max="53"/>
+    <col width="22" customWidth="1" min="54" max="54"/>
+    <col width="28" customWidth="1" min="55" max="55"/>
+    <col width="26" customWidth="1" min="56" max="56"/>
+    <col width="23" customWidth="1" min="57" max="57"/>
+    <col width="28" customWidth="1" min="58" max="58"/>
+    <col width="34" customWidth="1" min="59" max="59"/>
+    <col width="29" customWidth="1" min="60" max="60"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>team_key</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>global_player_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shot_attempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>shot_made</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>points_from_shots</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fg2a</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>fg2m</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fg2_pct</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>two_rate</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>three_rate</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>pts_per_shot</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>eligible_profile</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>top_zone_1</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>top_zone_2</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>top_zone_2_att</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>top_zone_2_pct</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>top_zone_3</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>top_zone_3_att</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>top_zone_3_pct</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>top_zone_1_qualified</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att_qualified</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct_qualified</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>top_zone_2_qualified</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>top_zone_2_att_qualified</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>top_zone_2_pct_qualified</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>top_zone_3_qualified</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>top_zone_3_att_qualified</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>top_zone_3_pct_qualified</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>top_zone_1_all</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att_all</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct_all</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>top_zone_2_all</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>top_zone_2_att_all</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>top_zone_2_pct_all</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>top_zone_3_all</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>top_zone_3_att_all</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>top_zone_3_pct_all</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>team_rank_shot_volume</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>team_rank_fg_pct</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>team_rank_pts_per_shot</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>team_rank_shot_volume_all</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>team_rank_fg_pct_all</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>team_rank_pts_per_shot_all</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume_all</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct_all</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>team_rank_fg_pct_qualified</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>team_rank_pts_per_shot_qualified</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct_qualified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FCP_T._BROPLEH</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>321972</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n">
+        <v>38</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>13</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>305553</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>23</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1.210526315789474</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>317922</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>65.4%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>8</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>900.0%</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>322305</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>1000.0%</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>321973</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="BG6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FCP_M._QUEIROZ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>154371</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>M. Queiroz</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>17</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AV7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FCP_G._DELGADO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>223738</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>G. Delgado</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AV8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>900.0%</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BG8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BH3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="26" customWidth="1" min="31" max="31"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="26" customWidth="1" min="34" max="34"/>
+    <col width="26" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="37" max="37"/>
+    <col width="26" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
     <col width="16" customWidth="1" min="45" max="45"/>
@@ -3112,107 +7100,107 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>13</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.583333333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.714285714285714</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>6</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="AE2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -3237,11 +7225,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -3259,23 +7247,23 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
         <v>2</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
-        <v>1</v>
-      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -3286,11 +7274,11 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -3305,20 +7293,20 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="BG2" t="n">
         <v>1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -3340,121 +7328,121 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
+          <t>FCP_X._WILLIAMS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>317922</t>
+          <t>305553</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C. Allen Williams</t>
+          <t>X. Williams</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1.210526315789474</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V3" t="n">
-        <v>5</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
       <c r="AE3" t="n">
         <v>5</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -3473,347 +7461,84 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="AQ3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
         <v>3</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AV3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>2</v>
       </c>
       <c r="AY3" t="n">
         <v>2</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>800.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
         <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
           <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BG3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Futebol Clube do Porto</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>FCP</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>FCP</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>FCP_C._DUNDAO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>322305</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>C. Dundao</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>27.3%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0.9090909090909091</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>5</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AV4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="BA4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BG4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sem dados</t>
         </is>
       </c>
     </row>
@@ -3979,41 +7704,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.612903225806452</v>
+        <v>1.159090909090909</v>
       </c>
       <c r="J2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4024,7 +7749,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4032,7 +7757,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -4040,7 +7765,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -4062,41 +7787,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="J3" t="n">
+        <v>42</v>
+      </c>
+      <c r="K3" t="n">
+        <v>33</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M3" t="n">
-        <v>7</v>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -4107,7 +7832,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -4115,7 +7840,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -4123,7 +7848,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4149,27 +7874,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K4" t="n">
         <v>8</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -4179,18 +7904,18 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -4198,11 +7923,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>500.0%</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4226,13 +7957,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4243,10 +7974,10 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -4256,18 +7987,18 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -4275,11 +8006,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4303,21 +8040,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -4326,14 +8063,14 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -4380,21 +8117,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -4403,14 +8140,14 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -4421,7 +8158,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -4429,7 +8166,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -4446,7 +8183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4601,27 +8338,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.612903225806452</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="J2" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -4631,14 +8368,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -4646,15 +8383,15 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -4680,68 +8417,234 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" t="n">
-        <v>21</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="E4" t="n">
+        <v>44</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17</v>
+      </c>
+      <c r="G4" t="n">
+        <v>51</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>38.6%</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.159090909090909</v>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M3" t="n">
-        <v>7</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>27.6%</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="L4" t="n">
+        <v>44</v>
+      </c>
+      <c r="M4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>29.7%</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>20.3%</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>600.0%</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>200.0%</t>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -4756,7 +8659,1443 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="29" customWidth="1" min="22" max="22"/>
+    <col width="38" customWidth="1" min="23" max="23"/>
+    <col width="35" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>team_key</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>global_player_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>attempts</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>made</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fg2a</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg2m</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>zone_share</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>eligible_zone_profile</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume_all</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct_all</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_volume_qualified</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>player_zone_rank_by_pct_qualified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FCP_T._BROPLEH</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>321972</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1.909090909090909</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>11</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>317922</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>317922</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FCP_G._DELGADO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>223738</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>G. Delgado</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>322305</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FCP_M._QUEIROZ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>154371</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>M. Queiroz</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FCP_T._OMLID</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>262570</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>T. Omlid</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FCP_T._BROPLEH</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>321972</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>T. Bropleh</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>322305</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FCP_C._DUNDAO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>322305</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>C. Dundao</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FCP_X._WILLIAMS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>305553</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>X. Williams</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>26.3%</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>500.0%</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FCP_J._WOODARD</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>321973</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>J. Woodard</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Futebol Clube do Porto</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FCP</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>317922</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>C. Allen Williams</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4925,56 +10264,56 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FCP_M._QUEIROZ</t>
+          <t>FCP_T._BROPLEH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>154371</t>
+          <t>321972</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M. Queiroz</t>
+          <t>T. Bropleh</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.666666666666667</v>
+        <v>1.909090909090909</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4985,7 +10324,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -4993,15 +10332,15 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>200.0%</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5023,46 +10362,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FCP_T._OMLID</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>262570</t>
+          <t>317922</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>T. Omlid</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M3" t="n">
         <v>8</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6</v>
-      </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -5072,7 +10411,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -5091,7 +10430,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -5121,17 +10460,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FCP_T._BROPLEH</t>
+          <t>FCP_C._ALLEN_WILLIAMS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>321972</t>
+          <t>317922</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>T. Bropleh</t>
+          <t>C. Allen Williams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5140,21 +10479,21 @@
         </is>
       </c>
       <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
         <v>6</v>
       </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -5163,14 +10502,14 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -5198,331 +10537,6 @@
       <c r="X4" t="inlineStr">
         <is>
           <t>200.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Futebol Clube do Porto</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>FCP</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>FCP</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>FCP_T._BROPLEH</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>321972</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>T. Bropleh</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>35.7%</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Futebol Clube do Porto</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FCP</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>FCP</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>FCP_C._DUNDAO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>322305</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>C. Dundao</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Futebol Clube do Porto</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FCP</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>FCP</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>FCP_C._ALLEN_WILLIAMS</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>317922</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>C. Allen Williams</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>41.7%</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>300.0%</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sem dados</t>
         </is>
       </c>
     </row>
